--- a/public/template_productos.xlsx
+++ b/public/template_productos.xlsx
@@ -19,7 +19,7 @@
     <t>nombre</t>
   </si>
   <si>
-    <t>Breve descripción del cesto de ropa.</t>
+    <t>descripcion_corta</t>
   </si>
   <si>
     <t>descripcion</t>
@@ -330,7 +330,7 @@
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
